--- a/boss_monsters.xlsx
+++ b/boss_monsters.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>IMAGE</t>
   </si>
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Whenever Adventurers gather, the Boss gathers as well and gains that much HP.</t>
   </si>
   <si>
-    <t>24/40/64/80</t>
+    <t>10/14/18/24</t>
   </si>
   <si>
     <t>—</t>
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t xml:space="preserve">If the Lich took no damage this turn, they return to full health.</t>
-  </si>
-  <si>
-    <t>20/28/52/60</t>
   </si>
 </sst>
 </file>
@@ -113,8 +110,11 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -617,7 +617,7 @@
     <col bestFit="1" min="1" max="1" width="28.421875"/>
     <col bestFit="1" min="2" max="2" width="13.421875"/>
     <col bestFit="1" min="3" max="3" width="91.421875"/>
-    <col bestFit="1" min="4" max="4" width="11.28125"/>
+    <col customWidth="1" min="4" max="4" width="14.00390625"/>
     <col bestFit="1" min="5" max="5" width="3.00390625"/>
     <col bestFit="1" min="6" max="6" width="10.8515625"/>
   </cols>
@@ -713,7 +713,7 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -721,6 +721,9 @@
       <c r="F5" t="s">
         <v>10</v>
       </c>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="D6" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
